--- a/docs/Files/ODYM_Tutorial6_Lifetime_V1.0_EVLIB.xlsx
+++ b/docs/Files/ODYM_Tutorial6_Lifetime_V1.0_EVLIB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02DD532-FDD8-46DA-BCC8-9097369F8F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A8100F-EA41-4AF0-9D91-FEBD36EEA965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -317,13 +317,13 @@
     <t>Lanphear</t>
   </si>
   <si>
-    <t>ODYM_Classifications_Master_EV_LIB</t>
-  </si>
-  <si>
     <t>EV LIB</t>
   </si>
   <si>
     <t>other EV LIB products</t>
+  </si>
+  <si>
+    <t>ODYM_Classifications_EV_LIB</t>
   </si>
 </sst>
 </file>
@@ -950,7 +950,7 @@
         <v>38</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>18</v>
@@ -1146,7 +1146,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>99</v>
+      </c>
+      <c r="B2">
+        <v>15</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1160,7 +1163,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>100</v>
+      </c>
+      <c r="B3">
+        <v>20</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
